--- a/artfynd/A 47295-2023 artfynd.xlsx
+++ b/artfynd/A 47295-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47295-2023 artfynd.xlsx
+++ b/artfynd/A 47295-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73885279</v>
+        <v>127803672</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nörder-Kotjärnberget, västra, Jmt</t>
+          <t>Bensjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523977.2713787286</v>
+        <v>524094</v>
       </c>
       <c r="R2" t="n">
-        <v>6950088.063376574</v>
+        <v>6949973</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -747,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Efter äldre stig.</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,84 +758,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93405832</v>
+        <v>127803671</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nörder-Kotjärnberget, Jmt</t>
+          <t>Bensjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524103.2039958651</v>
+        <v>524095</v>
       </c>
       <c r="R3" t="n">
-        <v>6950102.760610756</v>
+        <v>6949973</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,84 +859,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93405539</v>
+        <v>73885279</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nörder-Kotjärnberget, Jmt</t>
+          <t>Nörder-Kotjärnberget, västra, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523998.3334307432</v>
+        <v>523977</v>
       </c>
       <c r="R4" t="n">
-        <v>6950101.53743038</v>
+        <v>6950088</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,27 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid koordinaten ligger vindfälla som sågats av. Angivna fynd ligger från denna position och utefter stigen, ca 50 meter östlig riktning av stigen.</t>
+          <t>Efter äldre stig.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,65 +982,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>93405614</v>
+        <v>127803670</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nörder-Kotjärnberget, Jmt</t>
+          <t>Bensjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524141.5328875616</v>
+        <v>524094</v>
       </c>
       <c r="R5" t="n">
-        <v>6950082.369992765</v>
+        <v>6949975</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,84 +1065,70 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>93405581</v>
+        <v>127803676</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nörder-Kotjärnberget, Jmt</t>
+          <t>Bensjö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524181.3447626143</v>
+        <v>524241</v>
       </c>
       <c r="R6" t="n">
-        <v>6950173.611077349</v>
+        <v>6950071</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,22 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,19 +1166,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1303,12 +1187,7 @@
         <v>93405361</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523962.6521682572</v>
+        <v>523963</v>
       </c>
       <c r="R7" t="n">
-        <v>6950074.176804177</v>
+        <v>6950074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,19 +1264,9 @@
           <t>2021-05-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,6 +1291,864 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>93405539</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nörder-Kotjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>523998</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6950102</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid koordinaten ligger vindfälla som sågats av. Angivna fynd ligger från denna position och utefter stigen, ca 50 meter östlig riktning av stigen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>93405581</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nörder-Kotjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>524181</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6950174</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>93405614</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nörder-Kotjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524142</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6950082</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>93405703</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nörder-Kotjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524131</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6950058</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>93405832</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nörder-Kotjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>524103</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6950103</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127803677</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bensjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>524237</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6950092</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127803678</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bensjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>524254</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6950103</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127803679</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bensjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>524252</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6950118</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47295-2023 artfynd.xlsx
+++ b/artfynd/A 47295-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803671</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885279</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803670</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93405361</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93405539</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93405581</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93405614</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93405703</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93405832</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1947,6 +2007,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803677</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803678</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,8 +2219,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803679</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>